--- a/diseases/d045/2026-2029.xlsx
+++ b/diseases/d045/2026-2029.xlsx
@@ -18278,6 +18278,154 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>3</v>
+      </c>
+      <c r="O102" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr"/>
+      <c r="AT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18311,7 +18459,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -18394,7 +18542,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
@@ -18404,7 +18552,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11">
@@ -18456,7 +18604,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2370</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d045/2026-2029.xlsx
+++ b/diseases/d045/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1454,9 +1451,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1850,9 +1844,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2246,9 +2237,6 @@
       <c r="O10" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.01868976085656669</v>
       </c>
@@ -3382,9 +3370,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="S17" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3923,9 +3908,6 @@
       <c r="O20" t="n">
         <v>1</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -4319,9 +4301,6 @@
       <c r="O22" t="n">
         <v>1</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -4715,9 +4694,6 @@
       <c r="O24" t="n">
         <v>4</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.03737952171313338</v>
       </c>
@@ -5851,9 +5827,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="S31" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6392,9 +6365,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -6788,9 +6758,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7184,9 +7151,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -8172,9 +8136,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -8320,9 +8281,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="S45" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8861,9 +8819,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -9257,9 +9212,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -9653,9 +9605,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -10641,9 +10590,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -10789,9 +10735,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="S59" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11330,9 +11273,6 @@
       <c r="O62" t="n">
         <v>1</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -11726,9 +11666,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -12122,9 +12059,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -13258,9 +13192,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -13554,9 +13485,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -13950,9 +13878,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -14346,9 +14271,6 @@
       <c r="O79" t="n">
         <v>4</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.03737952171313338</v>
       </c>
@@ -14742,9 +14664,6 @@
       <c r="O81" t="n">
         <v>1</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -14890,9 +14809,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -15038,9 +14954,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -15186,9 +15099,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -15334,9 +15244,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -15482,9 +15389,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -15878,9 +15782,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -16274,9 +16175,6 @@
       <c r="O90" t="n">
         <v>1</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.009344880428283346</v>
       </c>
@@ -16670,9 +16568,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -16818,9 +16713,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -16966,9 +16858,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -17114,9 +17003,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -17262,9 +17148,6 @@
       <c r="O96" t="n">
         <v>1</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -17410,9 +17293,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -17558,9 +17438,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -17954,9 +17831,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -18349,9 +18223,6 @@
       </c>
       <c r="O102" t="n">
         <v>3</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>0</v>
       </c>
       <c r="R102" t="n">
         <v>0.002450425222697299</v>

--- a/diseases/d045/2026-2029.xlsx
+++ b/diseases/d045/2026-2029.xlsx
@@ -13293,12 +13293,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -13332,84 +13332,92 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>503</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>503</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0.0356001829194019</v>
+        <v>0</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ECHINOCOCCUS_MULTILOCULARIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ECHINOCOCCUS_MULTILOCULARIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13436,17 +13444,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -13485,17 +13493,34 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>SER_CA_ON_PHO_IDTO_ECHINOCOCCUS_MULTILOCULARIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ECHINOCOCCUS_MULTILOCULARIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Echinococcus Multilocularis Infection</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -13503,6 +13528,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary Echinococcus multilocularis infection notifications; confirmed cases only. This species-specific source category is narrower than the ontology's all-echinococcosis D045 concept.</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN75" t="b">
+        <v>1</v>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -13515,12 +13598,12 @@
       </c>
       <c r="AQ75" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_230</t>
+          <t>SER_CA_ON_PHO_IDTO_ECHINOCOCCUS_MULTILOCULARIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT75" t="n">
@@ -13528,47 +13611,47 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13595,17 +13678,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -13639,170 +13722,84 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>503</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>Echinococcus</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD76" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE76" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF76" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG76" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN76" t="b">
-        <v>1</v>
+        <v>503</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0.0356001829194019</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -13834,12 +13831,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -13888,7 +13885,7 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -13908,12 +13905,12 @@
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT77" t="n">
@@ -13921,47 +13918,47 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -13993,12 +13990,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -14039,22 +14036,22 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Ekinokokkose</t>
+          <t>Echinococcus</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
@@ -14079,7 +14076,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr">
@@ -14114,17 +14111,17 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -14142,12 +14139,12 @@
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT78" t="n">
@@ -14155,47 +14152,47 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -14227,12 +14224,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -14266,13 +14263,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>0.03737952171313338</v>
+        <v>0</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -14281,7 +14278,7 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -14306,7 +14303,7 @@
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT79" t="n">
@@ -14319,42 +14316,42 @@
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -14386,12 +14383,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -14425,29 +14422,29 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Echinokockinfektion</t>
+          <t>Ekinokokkose</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
@@ -14472,7 +14469,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr">
@@ -14507,17 +14504,17 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -14540,7 +14537,7 @@
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT80" t="n">
@@ -14553,42 +14550,42 @@
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -14620,12 +14617,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -14650,7 +14647,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -14659,81 +14656,95 @@
         </is>
       </c>
       <c r="N81" t="n">
+        <v>4</v>
+      </c>
+      <c r="O81" t="n">
+        <v>4</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0.03737952171313338</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="AT81" t="n">
         <v>1</v>
       </c>
-      <c r="O81" t="n">
-        <v>1</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP81" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr"/>
-      <c r="AT81" t="n">
-        <v>0</v>
-      </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -14760,17 +14771,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -14795,7 +14806,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -14804,81 +14815,170 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Echinokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN82" t="b">
+        <v>1</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -14940,7 +15040,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -14949,13 +15049,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -15085,7 +15185,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -15200,12 +15300,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -15230,12 +15330,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N85" t="n">
@@ -15278,42 +15378,42 @@
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15345,12 +15445,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -15375,12 +15475,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N86" t="n">
@@ -15397,82 +15497,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ86" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15499,17 +15585,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -15548,165 +15634,76 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>Echinococcus</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD87" t="inlineStr">
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr"/>
+      <c r="AT87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV87" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE87" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF87" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG87" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN87" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP87" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ87" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS87" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="AT87" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV87" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15738,12 +15735,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -15792,7 +15789,7 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -15812,12 +15809,12 @@
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT88" t="n">
@@ -15825,47 +15822,47 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -15897,12 +15894,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -15943,22 +15940,22 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ekinokokkose</t>
+          <t>Echinococcus</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
@@ -15983,7 +15980,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD89" t="inlineStr">
@@ -16018,17 +16015,17 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -16046,12 +16043,12 @@
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT89" t="n">
@@ -16059,47 +16056,47 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -16131,12 +16128,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -16170,13 +16167,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>0.009344880428283346</v>
+        <v>0</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -16185,7 +16182,7 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -16210,7 +16207,7 @@
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT90" t="n">
@@ -16223,42 +16220,42 @@
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -16290,12 +16287,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -16329,29 +16326,29 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Echinokockinfektion</t>
+          <t>Ekinokokkose</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
@@ -16376,7 +16373,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD91" t="inlineStr">
@@ -16411,17 +16408,17 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -16444,7 +16441,7 @@
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT91" t="n">
@@ -16457,42 +16454,42 @@
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -16524,12 +16521,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -16554,7 +16551,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -16563,81 +16560,95 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -16664,17 +16675,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -16699,7 +16710,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -16708,81 +16719,170 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="R93" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Echinokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN93" t="b">
+        <v>1</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -16844,7 +16944,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -16989,7 +17089,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -17134,7 +17234,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -17143,13 +17243,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -17249,12 +17349,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -17279,12 +17379,12 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N97" t="n">
@@ -17327,42 +17427,42 @@
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -17394,12 +17494,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -17424,104 +17524,90 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ98" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -17548,17 +17634,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -17597,165 +17683,76 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="W99" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>Echinococcus</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD99" t="inlineStr">
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr"/>
+      <c r="AT99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE99" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF99" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG99" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
-        </is>
-      </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN99" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP99" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="AT99" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV99" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17787,12 +17784,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -17841,7 +17838,7 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -17861,12 +17858,12 @@
       </c>
       <c r="AQ100" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT100" t="n">
@@ -17874,47 +17871,47 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -17946,12 +17943,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -17992,22 +17989,22 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>Ekinokokkose</t>
+          <t>Echinococcus</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr">
@@ -18032,7 +18029,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr">
@@ -18067,17 +18064,17 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -18095,12 +18092,12 @@
       </c>
       <c r="AQ101" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT101" t="n">
@@ -18108,47 +18105,47 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18180,118 +18177,511 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>Ekinokokkose</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN103" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>D045</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>Echinococcosis</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
         <is>
           <t>包虫病</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t>Parasitic</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N102" t="n">
+      <c r="N104" t="n">
         <v>3</v>
       </c>
-      <c r="O102" t="n">
+      <c r="O104" t="n">
         <v>3</v>
       </c>
-      <c r="R102" t="n">
+      <c r="R104" t="n">
         <v>0.002450425222697299</v>
       </c>
-      <c r="S102" t="inlineStr">
+      <c r="S104" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO102" t="inlineStr">
+      <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP102" t="inlineStr">
+      <c r="AP104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR102" t="inlineStr">
+      <c r="AR104" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS102" t="inlineStr"/>
-      <c r="AT102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU102" t="inlineStr">
+      <c r="AS104" t="inlineStr"/>
+      <c r="AT104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV102" t="inlineStr">
+      <c r="AV104" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW102" t="inlineStr">
+      <c r="AW104" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
+      <c r="AX104" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY102" t="inlineStr">
+      <c r="AY104" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
+      <c r="AZ104" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA102" t="inlineStr">
+      <c r="BA104" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB102" t="inlineStr">
+      <c r="BB104" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC102" t="inlineStr">
+      <c r="BC104" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -18413,7 +18803,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
@@ -18423,7 +18813,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11">
@@ -18443,7 +18833,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d045/2026-2029.xlsx
+++ b/diseases/d045/2026-2029.xlsx
@@ -18687,6 +18687,151 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr"/>
+      <c r="AT105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18720,7 +18865,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -18803,7 +18948,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -18813,7 +18958,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d045/2026-2029.xlsx
+++ b/diseases/d045/2026-2029.xlsx
@@ -15735,12 +15735,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -15774,95 +15774,84 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="O88" t="n">
+        <v>952</v>
+      </c>
+      <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>0.06737847741405686</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ88" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -15889,7 +15878,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -15938,98 +15927,23 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U89" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>Echinococcus</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD89" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE89" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF89" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG89" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN89" t="b">
-        <v>1</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -16123,17 +16037,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -16172,17 +16086,34 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="R90" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Echinococcus</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -16190,6 +16121,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN90" t="b">
+        <v>1</v>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -16202,12 +16191,12 @@
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT90" t="n">
@@ -16215,47 +16204,47 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -16282,7 +16271,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -16331,98 +16320,23 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U91" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>Ekinokokkose</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD91" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE91" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF91" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG91" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN91" t="b">
-        <v>1</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -16516,17 +16430,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -16560,29 +16474,104 @@
         </is>
       </c>
       <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Ekinokokkose</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN92" t="b">
         <v>1</v>
       </c>
-      <c r="O92" t="n">
-        <v>1</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0.009344880428283346</v>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -16600,7 +16589,7 @@
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+          <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
       <c r="AT92" t="n">
@@ -16613,42 +16602,42 @@
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -16675,7 +16664,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -16724,98 +16713,23 @@
       <c r="O93" t="n">
         <v>1</v>
       </c>
+      <c r="R93" t="n">
+        <v>0.009344880428283346</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U93" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
         </is>
       </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>Echinokockinfektion</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD93" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE93" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF93" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG93" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN93" t="b">
-        <v>1</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -16909,17 +16823,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -16944,7 +16858,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -16953,81 +16867,170 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="R94" t="n">
-        <v>0</v>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Echinokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN94" t="b">
+        <v>1</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ECHINOCOCCOSIS</t>
+        </is>
+      </c>
       <c r="AT94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -17089,7 +17092,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -17234,7 +17237,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -17379,7 +17382,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -17524,7 +17527,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -17533,13 +17536,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -17639,12 +17642,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -17669,22 +17672,22 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -17717,42 +17720,42 @@
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -17784,12 +17787,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -17836,82 +17839,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ100" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17927,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -17987,98 +17976,23 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U101" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_230</t>
-        </is>
-      </c>
-      <c r="W101" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Echinococcus</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD101" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE101" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF101" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG101" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN101" t="b">
-        <v>1</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -18172,17 +18086,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -18221,17 +18135,34 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="R102" t="n">
-        <v>0</v>
-      </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_230</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>Echinococcus</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -18239,6 +18170,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 230.</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN102" t="b">
+        <v>1</v>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -18251,12 +18240,12 @@
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
+          <t>SER_FI_THL_TTR_230</t>
         </is>
       </c>
       <c r="AT102" t="n">
@@ -18264,47 +18253,47 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18331,7 +18320,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -18380,98 +18369,23 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U103" t="inlineStr">
         <is>
           <t>SER_NO_FHI_405_MONTHLY</t>
         </is>
       </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_405_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W103" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X103" t="inlineStr">
-        <is>
-          <t>Ekinokokkose</t>
-        </is>
-      </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD103" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE103" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF103" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG103" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN103" t="b">
-        <v>1</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -18565,17 +18479,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -18600,7 +18514,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -18609,81 +18523,170 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>3</v>
-      </c>
-      <c r="R104" t="n">
-        <v>0.002450425222697299</v>
-      </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>Ekinokokkose</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN104" t="b">
+        <v>1</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_405_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18745,7 +18748,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -18754,13 +18757,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -18827,6 +18830,151 @@
         </is>
       </c>
       <c r="BC105" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr"/>
+      <c r="AT106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -18948,7 +19096,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -18958,7 +19106,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11">
@@ -19010,7 +19158,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2373</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d045/2026-2029.xlsx
+++ b/diseases/d045/2026-2029.xlsx
@@ -18980,6 +18980,151 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>echinococcosis</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>1</v>
+      </c>
+      <c r="O107" t="n">
+        <v>1</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr"/>
+      <c r="AT107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC107" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19013,7 +19158,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -19096,7 +19241,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -19106,7 +19251,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11">
@@ -19158,7 +19303,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3325</v>
+        <v>3326</v>
       </c>
     </row>
     <row r="16">
